--- a/backend/data/DSA1101_Sem1_2425_Quiz1.xlsx
+++ b/backend/data/DSA1101_Sem1_2425_Quiz1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhixin/Documents/y4s1/dsa3101/extracted_questions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhixin/Documents/y4s1/dsa3101/dsa3101-2510-quiz-02/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0C92F5F-81A7-C54B-970F-4EB484512F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCCD095-AC88-6645-8C61-BD9A6DCE0605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16660" activeTab="1" xr2:uid="{CA20E2D9-AC26-2B4B-A400-E03C0BFEE2BC}"/>
   </bookViews>
@@ -39,9 +39,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="39">
   <si>
-    <t>Context ID</t>
-  </si>
-  <si>
     <t>Context Text</t>
   </si>
   <si>
@@ -180,12 +177,15 @@
   <si>
     <t>Sub-Question Number</t>
   </si>
+  <si>
+    <t>Context ID</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -197,6 +197,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -219,12 +225,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -567,14 +574,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="76" customHeight="1" x14ac:dyDescent="0.2">
@@ -582,10 +589,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -606,53 +613,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="B1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" t="s">
-        <v>38</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" t="s">
-        <v>12</v>
-      </c>
       <c r="P1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -663,10 +670,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
         <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -675,16 +682,16 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" t="s">
-        <v>19</v>
-      </c>
       <c r="O2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="68" x14ac:dyDescent="0.2">
@@ -695,10 +702,10 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -707,16 +714,16 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="170" x14ac:dyDescent="0.2">
@@ -727,10 +734,10 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -739,16 +746,16 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" t="s">
         <v>18</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N4" t="s">
-        <v>19</v>
-      </c>
       <c r="O4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="170" x14ac:dyDescent="0.2">
@@ -759,10 +766,10 @@
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -771,16 +778,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" t="s">
         <v>18</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" t="s">
-        <v>19</v>
-      </c>
       <c r="O5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="51" x14ac:dyDescent="0.2">
@@ -791,10 +798,10 @@
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -803,16 +810,16 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="187" x14ac:dyDescent="0.2">
@@ -823,10 +830,10 @@
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -835,16 +842,16 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="119" x14ac:dyDescent="0.2">
@@ -855,10 +862,10 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -867,16 +874,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N8" t="s">
         <v>18</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="N8" t="s">
-        <v>19</v>
-      </c>
       <c r="O8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="68" x14ac:dyDescent="0.2">
@@ -887,10 +894,10 @@
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -899,13 +906,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
